--- a/docs/AutomationLabs_QA_TestSuite.xlsx
+++ b/docs/AutomationLabs_QA_TestSuite.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Fansub\Evidencias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83549B31-B01C-47C4-9EFC-24D1A53E8794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF4A8B4-4052-4E39-B88E-CE12F3F6A65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{EC87A7D6-B4AD-40EA-BD61-1278416F277F}"/>
   </bookViews>
@@ -584,9 +584,6 @@
     <t>TC-053</t>
   </si>
   <si>
-    <t>Los datos del producto se mantienen</t>
-  </si>
-  <si>
     <t>TC-054</t>
   </si>
   <si>
@@ -2117,6 +2114,9 @@
   </si>
   <si>
     <t>TC-037 Cantidad 0 en un producto.jpg</t>
+  </si>
+  <si>
+    <t>Datos del producto se conservan al llegar al checkout</t>
   </si>
 </sst>
 </file>
@@ -2517,7 +2517,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2545,13 +2545,13 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2562,7 +2562,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>12</v>
@@ -2579,13 +2579,13 @@
         <v>11</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2616,7 +2616,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>396</v>
@@ -2633,10 +2633,10 @@
         <v>25</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2650,7 +2650,7 @@
         <v>22</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>126</v>
@@ -2667,7 +2667,7 @@
         <v>24</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>129</v>
@@ -2684,7 +2684,7 @@
         <v>27</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>131</v>
@@ -2698,10 +2698,10 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>393</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>136</v>
@@ -2715,10 +2715,10 @@
         <v>15</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>137</v>
@@ -2732,10 +2732,10 @@
         <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>391</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>138</v>
@@ -2800,10 +2800,10 @@
         <v>33</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>145</v>
@@ -2840,7 +2840,7 @@
         <v>44</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2868,10 +2868,10 @@
         <v>33</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>401</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>163</v>
@@ -2888,7 +2888,7 @@
         <v>49</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>165</v>
@@ -2905,7 +2905,7 @@
         <v>149</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>148</v>
@@ -2919,10 +2919,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>168</v>
@@ -2930,7 +2930,7 @@
     </row>
     <row r="26" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>51</v>
@@ -2942,29 +2942,29 @@
         <v>52</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>51</v>
@@ -2976,29 +2976,29 @@
         <v>56</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>58</v>
@@ -3010,12 +3010,12 @@
         <v>60</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>58</v>
@@ -3027,12 +3027,12 @@
         <v>62</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>58</v>
@@ -3044,32 +3044,32 @@
         <v>64</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>407</v>
-      </c>
       <c r="E33" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>66</v>
@@ -3078,7 +3078,7 @@
         <v>67</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -3374,13 +3374,13 @@
         <v>78</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>79</v>
@@ -3392,10 +3392,10 @@
         <v>79</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -3409,23 +3409,23 @@
         <v>97</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K3" s="2"/>
     </row>
@@ -3440,25 +3440,25 @@
         <v>96</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K4" s="2"/>
     </row>
@@ -3473,25 +3473,25 @@
         <v>95</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K5" s="2"/>
     </row>
@@ -3506,25 +3506,25 @@
         <v>94</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K6" s="2"/>
     </row>
@@ -3539,25 +3539,25 @@
         <v>93</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K7" s="2"/>
     </row>
@@ -3572,25 +3572,25 @@
         <v>92</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>80</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K8" s="2"/>
     </row>
@@ -3605,25 +3605,25 @@
         <v>91</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K9" s="2"/>
     </row>
@@ -3638,25 +3638,25 @@
         <v>98</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K10" s="2"/>
     </row>
@@ -3668,31 +3668,31 @@
         <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I11" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3706,25 +3706,25 @@
         <v>102</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K12" s="2"/>
     </row>
@@ -3739,25 +3739,25 @@
         <v>104</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K13" s="2"/>
     </row>
@@ -3769,28 +3769,28 @@
         <v>5</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K14" s="2"/>
     </row>
@@ -3805,25 +3805,25 @@
         <v>107</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K15" s="2"/>
     </row>
@@ -3838,25 +3838,25 @@
         <v>109</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K16" s="2"/>
     </row>
@@ -3874,10 +3874,10 @@
         <v>112</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>113</v>
@@ -3886,13 +3886,13 @@
         <v>80</v>
       </c>
       <c r="I17" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -3903,26 +3903,26 @@
         <v>11</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>112</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K18" s="2"/>
     </row>
@@ -3940,22 +3940,22 @@
         <v>112</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K19" s="2"/>
     </row>
@@ -3973,22 +3973,22 @@
         <v>112</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>118</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K20" s="2"/>
     </row>
@@ -4006,22 +4006,22 @@
         <v>112</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K21" s="2"/>
     </row>
@@ -4033,28 +4033,28 @@
         <v>15</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>122</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K22" s="2"/>
     </row>
@@ -4066,16 +4066,16 @@
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>124</v>
@@ -4084,13 +4084,13 @@
         <v>89</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="75" x14ac:dyDescent="0.25">
@@ -4104,28 +4104,28 @@
         <v>19</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4139,13 +4139,13 @@
         <v>127</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>128</v>
@@ -4154,13 +4154,13 @@
         <v>89</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4174,13 +4174,13 @@
         <v>24</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>130</v>
@@ -4189,13 +4189,13 @@
         <v>89</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4209,13 +4209,13 @@
         <v>27</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>132</v>
@@ -4224,13 +4224,13 @@
         <v>89</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4241,16 +4241,16 @@
         <v>15</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>365</v>
-      </c>
       <c r="E28" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>135</v>
@@ -4259,13 +4259,13 @@
         <v>89</v>
       </c>
       <c r="I28" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="K28" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4276,31 +4276,31 @@
         <v>15</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.25">
@@ -4311,31 +4311,31 @@
         <v>15</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="75" x14ac:dyDescent="0.25">
@@ -4349,13 +4349,13 @@
         <v>139</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>142</v>
@@ -4364,13 +4364,13 @@
         <v>89</v>
       </c>
       <c r="I31" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="K31" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
@@ -4381,16 +4381,16 @@
         <v>134</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>141</v>
@@ -4402,10 +4402,10 @@
         <v>141</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="123.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4416,16 +4416,16 @@
         <v>33</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>144</v>
@@ -4434,10 +4434,10 @@
         <v>80</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K33" s="2"/>
     </row>
@@ -4452,28 +4452,28 @@
         <v>146</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>147</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4490,23 +4490,23 @@
         <v>122</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
         <v>150</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I35" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="K35" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="152.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4523,10 +4523,10 @@
         <v>167</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>153</v>
@@ -4535,13 +4535,13 @@
         <v>89</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="180" customHeight="1" x14ac:dyDescent="0.25">
@@ -4558,10 +4558,10 @@
         <v>167</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>156</v>
@@ -4570,13 +4570,13 @@
         <v>89</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4593,25 +4593,25 @@
         <v>167</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>80</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="164.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4622,16 +4622,16 @@
         <v>33</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>161</v>
@@ -4643,10 +4643,10 @@
         <v>161</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4657,28 +4657,28 @@
         <v>33</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>80</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K40" s="2"/>
     </row>
@@ -4690,16 +4690,16 @@
         <v>33</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>164</v>
@@ -4708,13 +4708,13 @@
         <v>80</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="183" customHeight="1" x14ac:dyDescent="0.25">
@@ -4725,16 +4725,16 @@
         <v>33</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>166</v>
@@ -4743,13 +4743,13 @@
         <v>80</v>
       </c>
       <c r="I42" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="K42" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="138" customHeight="1" x14ac:dyDescent="0.25">
@@ -4766,10 +4766,10 @@
         <v>167</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>170</v>
@@ -4778,10 +4778,10 @@
         <v>89</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K43" s="2"/>
     </row>
@@ -4793,28 +4793,28 @@
         <v>51</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K44" s="2"/>
     </row>
@@ -4826,28 +4826,28 @@
         <v>51</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K45" s="2"/>
     </row>
@@ -4859,28 +4859,28 @@
         <v>51</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K46" s="2"/>
     </row>
@@ -4892,31 +4892,31 @@
         <v>51</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="165" x14ac:dyDescent="0.25">
@@ -4927,28 +4927,28 @@
         <v>51</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K48" s="2"/>
     </row>
@@ -4960,31 +4960,31 @@
         <v>51</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="184.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4995,28 +4995,28 @@
         <v>51</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K50" s="2"/>
     </row>
@@ -5028,28 +5028,28 @@
         <v>51</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K51" s="2"/>
     </row>
@@ -5061,28 +5061,28 @@
         <v>51</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K52" s="2"/>
     </row>
@@ -5094,28 +5094,28 @@
         <v>51</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K53" s="2"/>
     </row>
@@ -5127,86 +5127,86 @@
         <v>51</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="139.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>182</v>
+        <v>538</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>80</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="201" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>167</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>166</v>
@@ -5215,101 +5215,101 @@
         <v>80</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="185.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K57" s="2"/>
     </row>
     <row r="58" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>80</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>166</v>
@@ -5318,116 +5318,116 @@
         <v>80</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="180.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C61" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>80</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K61" s="2"/>
     </row>
     <row r="62" spans="1:11" ht="178.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="K62" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="J62" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="K62" s="2" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -7591,7 +7591,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>68</v>
@@ -7600,13 +7600,13 @@
         <v>73</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>72</v>
@@ -7623,7 +7623,7 @@
     </row>
     <row r="2" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>99</v>
@@ -7638,33 +7638,33 @@
         <v>80</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>377</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>80</v>
@@ -7679,16 +7679,16 @@
         <v>158</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
